--- a/Lane-Change/test/Results_Bogus_Attacker_V2.xlsx
+++ b/Lane-Change/test/Results_Bogus_Attacker_V2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>AttackType</t>
   </si>
@@ -152,6 +152,78 @@
   </si>
   <si>
     <t>Case 3</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Bogus</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Bogus</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Bogus</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Case 1</t>
+  </si>
+  <si>
+    <t>V4</t>
+  </si>
+  <si>
+    <t>Bogus</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V1</t>
+  </si>
+  <si>
+    <t>Bogus</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Case 2</t>
+  </si>
+  <si>
+    <t>V3</t>
+  </si>
+  <si>
+    <t>Bogus</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>Case 2</t>
   </si>
   <si>
     <t>V4</t>
@@ -560,7 +632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.26953125" customWidth="true"/>
@@ -1742,6 +1814,180 @@
       <c r="J40" s="0"/>
       <c r="K40" s="0"/>
     </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D41" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0.072594195471827785</v>
+      </c>
+      <c r="F41" s="0">
+        <v>0.0042168543690600246</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0.0241835761606779</v>
+      </c>
+      <c r="H41" s="0">
+        <v>0.0033321504600078277</v>
+      </c>
+      <c r="I41" s="0"/>
+      <c r="J41" s="0"/>
+      <c r="K41" s="0"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="C42" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="D42" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="E42" s="0">
+        <v>0.69102514444360574</v>
+      </c>
+      <c r="F42" s="0">
+        <v>0.0043673251405805498</v>
+      </c>
+      <c r="G42" s="0">
+        <v>1.0371236128952805</v>
+      </c>
+      <c r="H42" s="0">
+        <v>0.004381997956898781</v>
+      </c>
+      <c r="I42" s="0"/>
+      <c r="J42" s="0"/>
+      <c r="K42" s="0"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="E43" s="0">
+        <v>0.072833156703893454</v>
+      </c>
+      <c r="F43" s="0">
+        <v>0.0042066280201350616</v>
+      </c>
+      <c r="G43" s="0">
+        <v>0.031364258592784987</v>
+      </c>
+      <c r="H43" s="0">
+        <v>0.0046251974606342817</v>
+      </c>
+      <c r="I43" s="0"/>
+      <c r="J43" s="0"/>
+      <c r="K43" s="0"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="0" t="s">
+        <v>179</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="C44" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="D44" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" s="0">
+        <v>0.084284020509147281</v>
+      </c>
+      <c r="F44" s="0">
+        <v>0.0043353734154722096</v>
+      </c>
+      <c r="G44" s="0">
+        <v>0.025031635974666632</v>
+      </c>
+      <c r="H44" s="0">
+        <v>0.0034298138985919178</v>
+      </c>
+      <c r="I44" s="0"/>
+      <c r="J44" s="0"/>
+      <c r="K44" s="0"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>184</v>
+      </c>
+      <c r="C45" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="0" t="s">
+        <v>186</v>
+      </c>
+      <c r="E45" s="0">
+        <v>0.43216350459518277</v>
+      </c>
+      <c r="F45" s="0">
+        <v>0.0037694107634647822</v>
+      </c>
+      <c r="G45" s="0">
+        <v>0.55512646592200066</v>
+      </c>
+      <c r="H45" s="0">
+        <v>0.0046448105220456238</v>
+      </c>
+      <c r="I45" s="0"/>
+      <c r="J45" s="0"/>
+      <c r="K45" s="0"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" s="0">
+        <v>0.084444022458558685</v>
+      </c>
+      <c r="F46" s="0">
+        <v>0.004173906031739419</v>
+      </c>
+      <c r="G46" s="0">
+        <v>0.028275900382296881</v>
+      </c>
+      <c r="H46" s="0">
+        <v>0.0045175327597000185</v>
+      </c>
+      <c r="I46" s="0"/>
+      <c r="J46" s="0"/>
+      <c r="K46" s="0"/>
+    </row>
   </sheetData>
 </worksheet>
 </file>